--- a/ExpLogs/251124_1800/Result.xlsx
+++ b/ExpLogs/251124_1800/Result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuu53\Projects\Research_Master\force_plate\ExpLogs\251124_1800\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F25DB5AB-B982-4E18-8732-BE26D617FE05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65AA7E9A-4324-44F5-8CCB-29AAC8A6E2FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{2438DD00-2094-44D1-800B-5E5E3A4374CD}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="11">
   <si>
     <t>平面着地衝撃力</t>
     <rPh sb="0" eb="4">
@@ -98,6 +98,70 @@
     <t>踵接地時 [N]</t>
     <rPh sb="0" eb="4">
       <t>カカトセッチジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メモ：接地間隔[step]</t>
+    <rPh sb="3" eb="5">
+      <t>セッチ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カンカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最大値</t>
+    <rPh sb="0" eb="3">
+      <t>サイダイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最小値</t>
+    <rPh sb="0" eb="3">
+      <t>サイショウチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Excelだと小数点以下が０の数値は整数値として表示されるが，センサ＆プログラムのＦＢ値は1,0とか小数点以下第１位に０が入った実数値になっているっぽいので注意</t>
+    <rPh sb="7" eb="12">
+      <t>ショウスウテンイカ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>スウチ</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>セイスウチ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>チ</t>
+    </rPh>
+    <rPh sb="50" eb="53">
+      <t>ショウスウテン</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="64" eb="67">
+      <t>ジッスウチ</t>
+    </rPh>
+    <rPh sb="78" eb="80">
+      <t>チュウイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -106,8 +170,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="180" formatCode="0.000"/>
+  <numFmts count="2">
+    <numFmt numFmtId="176" formatCode="0.000"/>
+    <numFmt numFmtId="180" formatCode="0.0"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -134,7 +199,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -142,17 +207,437 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -489,200 +974,380 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3A555C-5D63-4691-8849-6A1640474937}">
-  <dimension ref="A3:F17"/>
+  <dimension ref="A2:H21"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="13.19921875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.5" customWidth="1"/>
+    <col min="6" max="6" width="12.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
+    <row r="2" spans="1:8" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="3" spans="1:8" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A3" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="D3" t="s">
+      <c r="B3" s="10"/>
+      <c r="D3" s="9" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B4" t="s">
+      <c r="E3" s="11"/>
+      <c r="F3" s="10"/>
+    </row>
+    <row r="4" spans="1:8" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="22"/>
+      <c r="B4" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="E4" t="s">
+      <c r="D4" s="22"/>
+      <c r="E4" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="8" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A5">
+      <c r="H4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A5" s="23">
         <v>1</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="13">
         <v>6.6</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="23">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A6">
+      <c r="E5" s="19">
+        <v>2.8</v>
+      </c>
+      <c r="F5" s="1">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="H5" s="23">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A6" s="24">
         <v>2</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="14">
         <v>7.4</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="24">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A7">
+      <c r="E6" s="20">
+        <v>2.6</v>
+      </c>
+      <c r="F6" s="5">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H6" s="24">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A7" s="24">
         <v>3</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="14">
         <v>7.1</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="24">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A8">
+      <c r="E7" s="20">
+        <v>2.8</v>
+      </c>
+      <c r="F7" s="29">
+        <v>3</v>
+      </c>
+      <c r="H7" s="24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A8" s="24">
         <v>4</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="14">
         <v>7.1</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="24">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A9">
+      <c r="E8" s="20">
+        <v>2.8</v>
+      </c>
+      <c r="F8" s="5">
+        <v>2.1</v>
+      </c>
+      <c r="H8" s="24">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A9" s="24">
         <v>5</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="14">
         <v>6.7</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="24">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A10">
+      <c r="E9" s="20">
+        <v>2.7</v>
+      </c>
+      <c r="F9" s="5">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H9" s="24">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A10" s="24">
         <v>6</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="14">
         <v>7.4</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="24">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A11">
+      <c r="E10" s="20">
+        <v>1.9</v>
+      </c>
+      <c r="F10" s="5">
+        <v>2.8</v>
+      </c>
+      <c r="H10" s="24">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A11" s="24">
         <v>7</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="14">
         <v>6.7</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="24">
         <v>7</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A12">
+      <c r="E11" s="20">
+        <v>3.3</v>
+      </c>
+      <c r="F11" s="5">
+        <v>2.7</v>
+      </c>
+      <c r="H11" s="24">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A12" s="24">
         <v>8</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="14">
         <v>6.4</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="24">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A13">
+      <c r="E12" s="20">
+        <v>2.5</v>
+      </c>
+      <c r="F12" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="H12" s="24">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A13" s="24">
         <v>9</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="14">
         <v>7.4</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="24">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A14">
+      <c r="E13" s="28">
+        <v>3</v>
+      </c>
+      <c r="F13" s="5">
+        <v>2.4</v>
+      </c>
+      <c r="H13" s="24">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A14" s="25">
         <v>10</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="15">
         <v>7.2</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="25">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
+      <c r="E14" s="21">
+        <v>2.9</v>
+      </c>
+      <c r="F14" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="H14" s="27">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A15" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="16">
         <f>AVERAGE($B$5:$B$14)</f>
         <v>7</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="E15" t="e">
+      <c r="E15" s="30">
         <f>AVERAGE(E$5:E$14)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F15" t="e">
+        <v>2.7299999999999995</v>
+      </c>
+      <c r="F15" s="6">
         <f>AVERAGE(F$5:F$14)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
+        <v>2.5300000000000002</v>
+      </c>
+      <c r="G15" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="H15" s="32">
+        <f>AVERAGE(H$5:H$14)</f>
+        <v>93.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A16" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="17">
         <f>MEDIAN($B$5:$B$14)</f>
         <v>7.1</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="E16" t="e">
+      <c r="E16" s="31">
         <f>MEDIAN(E$5:E$14)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="F16" t="e">
+        <v>2.8</v>
+      </c>
+      <c r="F16" s="7">
         <f>MEDIAN(F$5:F$14)</f>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="G16" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="H16" s="33">
+        <f>MEDIAN(H$5:H$14)</f>
+        <v>93.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A17" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="17">
         <f>_xlfn.STDEV.P($B$5:$B$14)</f>
         <v>0.35213633723318022</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="E17" t="e">
+      <c r="E17" s="31">
         <f>_xlfn.STDEV.P(E$5:E$14)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F17" t="e">
+        <v>0.34655446902327064</v>
+      </c>
+      <c r="F17" s="7">
         <f>_xlfn.STDEV.P(F$5:F$14)</f>
-        <v>#DIV/0!</v>
+        <v>0.33481338085566298</v>
+      </c>
+      <c r="G17" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="H17" s="34">
+        <f>_xlfn.STDEV.P(H$5:H$14)</f>
+        <v>6.1514225996918794</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A18" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="14">
+        <f>MAX(B$5:B$14)</f>
+        <v>7.4</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="4">
+        <f>MAX(E$5:E$14)</f>
+        <v>3.3</v>
+      </c>
+      <c r="F18" s="5">
+        <f>MAX(F$5:F$14)</f>
+        <v>3.1</v>
+      </c>
+      <c r="G18" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="24">
+        <f>MAX(H$5:H$14)</f>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A19" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="15">
+        <f>MIN(B$5:B$14)</f>
+        <v>6.4</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="2">
+        <f>MIN(E$5:E$14)</f>
+        <v>1.9</v>
+      </c>
+      <c r="F19" s="3">
+        <f>MIN(F$5:F$14)</f>
+        <v>2.1</v>
+      </c>
+      <c r="G19" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" s="25">
+        <f>MIN(H$5:H$14)</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="D21" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
